--- a/INSTANCES/instances_xlsx/A_MTN_8/231FL_10A_5.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_8/231FL_10A_5.xlsx
@@ -7704,7 +7704,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -7755,7 +7755,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
